--- a/data/nzd0486/nzd0486.xlsx
+++ b/data/nzd0486/nzd0486.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E503"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10995,6 +10995,48 @@
       <c r="E503" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="C504" t="n">
+        <v>351.72</v>
+      </c>
+      <c r="D504" t="n">
+        <v>361</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>347.01</v>
+      </c>
+      <c r="C505" t="n">
+        <v>351.41</v>
+      </c>
+      <c r="D505" t="n">
+        <v>360.76</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B667"/>
+  <dimension ref="A1:B669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17682,6 +17724,26 @@
       </c>
       <c r="B667" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -17850,28 +17912,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.108290595616003</v>
+        <v>-0.1086690778313574</v>
       </c>
       <c r="J2" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K2" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04539253309259139</v>
+        <v>0.04605764475241281</v>
       </c>
       <c r="M2" t="n">
-        <v>2.724392181631645</v>
+        <v>2.715395734471498</v>
       </c>
       <c r="N2" t="n">
-        <v>11.66949683434727</v>
+        <v>11.62403401537885</v>
       </c>
       <c r="O2" t="n">
-        <v>3.416064524324339</v>
+        <v>3.409403762445693</v>
       </c>
       <c r="P2" t="n">
-        <v>350.2311308922591</v>
+        <v>350.2355120753429</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17928,28 +17990,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1122247265893415</v>
+        <v>-0.110504656413976</v>
       </c>
       <c r="J3" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K3" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06380401702443084</v>
+        <v>0.06235662085850591</v>
       </c>
       <c r="M3" t="n">
-        <v>2.374657820328688</v>
+        <v>2.373826681395068</v>
       </c>
       <c r="N3" t="n">
-        <v>8.744321173446743</v>
+        <v>8.726513776203308</v>
       </c>
       <c r="O3" t="n">
-        <v>2.957079838869208</v>
+        <v>2.95406732763546</v>
       </c>
       <c r="P3" t="n">
-        <v>352.4454500959091</v>
+        <v>352.4255369746327</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18006,28 +18068,28 @@
         <v>0.0883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06071628399282914</v>
+        <v>0.06090884384434893</v>
       </c>
       <c r="J4" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K4" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01566471202669917</v>
+        <v>0.01589204334433603</v>
       </c>
       <c r="M4" t="n">
-        <v>2.648807939968261</v>
+        <v>2.639236914111121</v>
       </c>
       <c r="N4" t="n">
-        <v>10.97875140182093</v>
+        <v>10.93536942439655</v>
       </c>
       <c r="O4" t="n">
-        <v>3.313419895186986</v>
+        <v>3.306867010388618</v>
       </c>
       <c r="P4" t="n">
-        <v>359.0469348040978</v>
+        <v>359.0447073074095</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18065,7 +18127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E503"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31645,6 +31707,60 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-45.36910085936594,170.86462772267276</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-45.36970156277918,170.8646970926398</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-45.37023859137254,170.86513622603067</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-45.369100874720985,170.8646298927422</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-45.36970205550705,170.864693197441</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-45.370239356090764,170.86513336070678</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0486/nzd0486.xlsx
+++ b/data/nzd0486/nzd0486.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E505"/>
+  <dimension ref="A1:E506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11037,6 +11037,27 @@
       <c r="E505" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>346.77</v>
+      </c>
+      <c r="C506" t="n">
+        <v>351.04</v>
+      </c>
+      <c r="D506" t="n">
+        <v>360.52</v>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B669"/>
+  <dimension ref="A1:B670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17744,6 +17765,16 @@
       </c>
       <c r="B669" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -17912,28 +17943,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1086690778313574</v>
+        <v>-0.1089176990784811</v>
       </c>
       <c r="J2" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K2" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04605764475241281</v>
+        <v>0.04644053589053043</v>
       </c>
       <c r="M2" t="n">
-        <v>2.715395734471498</v>
+        <v>2.711200475222478</v>
       </c>
       <c r="N2" t="n">
-        <v>11.62403401537885</v>
+        <v>11.60172057208965</v>
       </c>
       <c r="O2" t="n">
-        <v>3.409403762445693</v>
+        <v>3.406129852499704</v>
       </c>
       <c r="P2" t="n">
-        <v>350.2355120753429</v>
+        <v>350.238398002469</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17990,28 +18021,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.110504656413976</v>
+        <v>-0.1098676784877751</v>
       </c>
       <c r="J3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06235662085850591</v>
+        <v>0.06189503325707713</v>
       </c>
       <c r="M3" t="n">
-        <v>2.373826681395068</v>
+        <v>2.372296730649957</v>
       </c>
       <c r="N3" t="n">
-        <v>8.726513776203308</v>
+        <v>8.713857572981816</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95406732763546</v>
+        <v>2.951924384699211</v>
       </c>
       <c r="P3" t="n">
-        <v>352.4255369746327</v>
+        <v>352.4181431098798</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18068,28 +18099,28 @@
         <v>0.0883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06090884384434893</v>
+        <v>0.06085555292080495</v>
       </c>
       <c r="J4" t="n">
+        <v>505</v>
+      </c>
+      <c r="K4" t="n">
         <v>504</v>
       </c>
-      <c r="K4" t="n">
-        <v>503</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01589204334433603</v>
+        <v>0.01592983365551348</v>
       </c>
       <c r="M4" t="n">
-        <v>2.639236914111121</v>
+        <v>2.63424265011483</v>
       </c>
       <c r="N4" t="n">
-        <v>10.93536942439655</v>
+        <v>10.91370470597502</v>
       </c>
       <c r="O4" t="n">
-        <v>3.306867010388618</v>
+        <v>3.303589669734276</v>
       </c>
       <c r="P4" t="n">
-        <v>359.0447073074095</v>
+        <v>359.0453256682849</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18127,7 +18158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E505"/>
+  <dimension ref="A1:E506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31761,6 +31792,33 @@
         </is>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-45.36910085304327,170.8646268291148</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-45.36970264360142,170.86468854833268</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-45.37024012080889,170.8651304953828</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0486/nzd0486.xlsx
+++ b/data/nzd0486/nzd0486.xlsx
@@ -11072,7 +11072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17775,6 +17775,26 @@
       </c>
       <c r="B670" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0486/nzd0486.xlsx
+++ b/data/nzd0486/nzd0486.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E506"/>
+  <dimension ref="A1:E509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11058,6 +11058,69 @@
       <c r="E506" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>348.41</v>
+      </c>
+      <c r="C507" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="D507" t="n">
+        <v>360.95</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>346.05</v>
+      </c>
+      <c r="C508" t="n">
+        <v>349.84</v>
+      </c>
+      <c r="D508" t="n">
+        <v>358.81</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>345.56</v>
+      </c>
+      <c r="C509" t="n">
+        <v>349.28</v>
+      </c>
+      <c r="D509" t="n">
+        <v>358.28</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B672"/>
+  <dimension ref="A1:B675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17795,6 +17858,36 @@
       </c>
       <c r="B672" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -17963,28 +18056,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1089176990784811</v>
+        <v>-0.1097576628116329</v>
       </c>
       <c r="J2" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K2" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04644053589053043</v>
+        <v>0.0476554226601118</v>
       </c>
       <c r="M2" t="n">
-        <v>2.711200475222478</v>
+        <v>2.703298088759781</v>
       </c>
       <c r="N2" t="n">
-        <v>11.60172057208965</v>
+        <v>11.54491422609153</v>
       </c>
       <c r="O2" t="n">
-        <v>3.406129852499704</v>
+        <v>3.397780779581215</v>
       </c>
       <c r="P2" t="n">
-        <v>350.238398002469</v>
+        <v>350.2482292491545</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18041,28 +18134,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1098676784877751</v>
+        <v>-0.10865249165981</v>
       </c>
       <c r="J3" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K3" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06189503325707713</v>
+        <v>0.06124103661729541</v>
       </c>
       <c r="M3" t="n">
-        <v>2.372296730649957</v>
+        <v>2.365178841756025</v>
       </c>
       <c r="N3" t="n">
-        <v>8.713857572981816</v>
+        <v>8.678210209763648</v>
       </c>
       <c r="O3" t="n">
-        <v>2.951924384699211</v>
+        <v>2.945880209676498</v>
       </c>
       <c r="P3" t="n">
-        <v>352.4181431098798</v>
+        <v>352.403949071658</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18119,28 +18212,28 @@
         <v>0.0883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06085555292080495</v>
+        <v>0.0592148727648489</v>
       </c>
       <c r="J4" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K4" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01592983365551348</v>
+        <v>0.01526090984948458</v>
       </c>
       <c r="M4" t="n">
-        <v>2.63424265011483</v>
+        <v>2.627276229562935</v>
       </c>
       <c r="N4" t="n">
-        <v>10.91370470597502</v>
+        <v>10.86710745129385</v>
       </c>
       <c r="O4" t="n">
-        <v>3.303589669734276</v>
+        <v>3.296529607222397</v>
       </c>
       <c r="P4" t="n">
-        <v>359.0453256682849</v>
+        <v>359.0645106148033</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18178,7 +18271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E506"/>
+  <dimension ref="A1:E509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31839,6 +31932,87 @@
         </is>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-45.369101001172645,170.8646477639022</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-45.36970060911194,170.86470463173407</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-45.37023875068884,170.8651356290882</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-45.36910078800966,170.86461763823257</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-45.36970455093325,170.86467347014292</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-45.3702455694235,170.86511007994739</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-45.369100743750245,170.86461138332666</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-45.36970544102074,170.864666433654</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-45.370247258174665,170.86510375235554</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0486/nzd0486.xlsx
+++ b/data/nzd0486/nzd0486.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E509"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11119,6 +11119,90 @@
         <v>358.28</v>
       </c>
       <c r="E509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>344.92</v>
+      </c>
+      <c r="C510" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="D510" t="n">
+        <v>357.65</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>344.92</v>
+      </c>
+      <c r="C511" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="D511" t="n">
+        <v>360.55</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>341.54</v>
+      </c>
+      <c r="C512" t="n">
+        <v>346.01</v>
+      </c>
+      <c r="D512" t="n">
+        <v>358.24</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>340.96</v>
+      </c>
+      <c r="C513" t="n">
+        <v>345.92</v>
+      </c>
+      <c r="D513" t="n">
+        <v>357.68</v>
+      </c>
+      <c r="E513" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11135,7 +11219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B675"/>
+  <dimension ref="A1:B680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17888,6 +17972,56 @@
       </c>
       <c r="B675" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -18056,28 +18190,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1097576628116329</v>
+        <v>-0.1166774710039313</v>
       </c>
       <c r="J2" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K2" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0476554226601118</v>
+        <v>0.05365020325070458</v>
       </c>
       <c r="M2" t="n">
-        <v>2.703298088759781</v>
+        <v>2.714273485136825</v>
       </c>
       <c r="N2" t="n">
-        <v>11.54491422609153</v>
+        <v>11.61842193868742</v>
       </c>
       <c r="O2" t="n">
-        <v>3.397780779581215</v>
+        <v>3.408580634030449</v>
       </c>
       <c r="P2" t="n">
-        <v>350.2482292491545</v>
+        <v>350.3293582216439</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18134,28 +18268,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.10865249165981</v>
+        <v>-0.1121629583003457</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K3" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06124103661729541</v>
+        <v>0.06566500566650335</v>
       </c>
       <c r="M3" t="n">
-        <v>2.365178841756025</v>
+        <v>2.362497538243295</v>
       </c>
       <c r="N3" t="n">
-        <v>8.678210209763648</v>
+        <v>8.660846632309664</v>
       </c>
       <c r="O3" t="n">
-        <v>2.945880209676498</v>
+        <v>2.942931639081965</v>
       </c>
       <c r="P3" t="n">
-        <v>352.403949071658</v>
+        <v>352.4451161371551</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18212,28 +18346,28 @@
         <v>0.0883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0592148727648489</v>
+        <v>0.05577425580318062</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="K4" t="n">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01526090984948458</v>
+        <v>0.01373093841671547</v>
       </c>
       <c r="M4" t="n">
-        <v>2.627276229562935</v>
+        <v>2.622370846479491</v>
       </c>
       <c r="N4" t="n">
-        <v>10.86710745129385</v>
+        <v>10.82717725140496</v>
       </c>
       <c r="O4" t="n">
-        <v>3.296529607222397</v>
+        <v>3.290467634152471</v>
       </c>
       <c r="P4" t="n">
-        <v>359.0645106148033</v>
+        <v>359.1048230233747</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18271,7 +18405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E509"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32013,6 +32147,114 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-45.369100685941525,170.86460321365365</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-45.36970626753015,170.86465989977128</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-45.370249265557625,170.86509623087795</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-45.369100685941525,170.86460321365365</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-45.36970626753015,170.86465989977128</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-45.37024002521914,170.8651308535483</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-45.3691003806295,170.86456006756873</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-45.36971063848716,170.8646253455809</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-45.370247385627565,170.86510327480144</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-45.36910032823704,170.8645526638028</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-45.369710781536476,170.8646242147164</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-45.37024916996796,170.86509658904353</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0486/nzd0486.xlsx
+++ b/data/nzd0486/nzd0486.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11203,6 +11203,111 @@
         <v>357.68</v>
       </c>
       <c r="E513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>340.27</v>
+      </c>
+      <c r="C514" t="n">
+        <v>345.6</v>
+      </c>
+      <c r="D514" t="n">
+        <v>356.99</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>340.44</v>
+      </c>
+      <c r="C515" t="n">
+        <v>345.71</v>
+      </c>
+      <c r="D515" t="n">
+        <v>357.01</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>340.97</v>
+      </c>
+      <c r="C516" t="n">
+        <v>345.43</v>
+      </c>
+      <c r="D516" t="n">
+        <v>356.95</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>342.08</v>
+      </c>
+      <c r="C517" t="n">
+        <v>346.2</v>
+      </c>
+      <c r="D517" t="n">
+        <v>357.61</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>343.18</v>
+      </c>
+      <c r="C518" t="n">
+        <v>347.49</v>
+      </c>
+      <c r="D518" t="n">
+        <v>358.25</v>
+      </c>
+      <c r="E518" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11219,7 +11324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B680"/>
+  <dimension ref="A1:B686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18022,6 +18127,66 @@
       </c>
       <c r="B680" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -18190,28 +18355,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1166774710039313</v>
+        <v>-0.1282939670141787</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="K2" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05365020325070458</v>
+        <v>0.06367880092838796</v>
       </c>
       <c r="M2" t="n">
-        <v>2.714273485136825</v>
+        <v>2.742059607437085</v>
       </c>
       <c r="N2" t="n">
-        <v>11.61842193868742</v>
+        <v>11.83649032207724</v>
       </c>
       <c r="O2" t="n">
-        <v>3.408580634030449</v>
+        <v>3.44042007930387</v>
       </c>
       <c r="P2" t="n">
-        <v>350.3293582216439</v>
+        <v>350.4659525482263</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18268,28 +18433,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1121629583003457</v>
+        <v>-0.1188702491798933</v>
       </c>
       <c r="J3" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="K3" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06566500566650335</v>
+        <v>0.07367701254891978</v>
       </c>
       <c r="M3" t="n">
-        <v>2.362497538243295</v>
+        <v>2.369818857957365</v>
       </c>
       <c r="N3" t="n">
-        <v>8.660846632309664</v>
+        <v>8.688749558962389</v>
       </c>
       <c r="O3" t="n">
-        <v>2.942931639081965</v>
+        <v>2.947668495432007</v>
       </c>
       <c r="P3" t="n">
-        <v>352.4451161371551</v>
+        <v>352.5239863500757</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18346,28 +18511,28 @@
         <v>0.0883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05577425580318062</v>
+        <v>0.04933470752242481</v>
       </c>
       <c r="J4" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="K4" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01373093841671547</v>
+        <v>0.01089503225904076</v>
       </c>
       <c r="M4" t="n">
-        <v>2.622370846479491</v>
+        <v>2.626317037410475</v>
       </c>
       <c r="N4" t="n">
-        <v>10.82717725140496</v>
+        <v>10.82289606742831</v>
       </c>
       <c r="O4" t="n">
-        <v>3.290467634152471</v>
+        <v>3.289817026436016</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1048230233747</v>
+        <v>359.1805227621866</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18405,7 +18570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32255,6 +32420,141 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-45.36910026590745,170.8645438558744</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-45.36971129015621,170.86462019386482</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-45.370251368529715,170.8650883512342</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-45.36910028126408,170.86454602594372</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-45.3697111153182,170.86462157603253</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-45.370251304803304,170.86508859001128</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-45.36910032914036,170.86455279145395</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-45.369711560360365,170.86461805778737</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-45.37025149598256,170.86508787367998</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-45.36910042940825,170.86456696073017</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-45.3697103364941,170.86462773296148</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-45.370249393010496,170.8650957533238</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-45.36910052877109,170.86458100235538</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-45.369708286118886,170.86464394201852</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-45.370247353764334,170.86510339418993</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0486/nzd0486.xlsx
+++ b/data/nzd0486/nzd0486.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E518"/>
+  <dimension ref="A1:E520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11308,6 +11308,48 @@
         <v>358.25</v>
       </c>
       <c r="E518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>343.39</v>
+      </c>
+      <c r="C519" t="n">
+        <v>347.06</v>
+      </c>
+      <c r="D519" t="n">
+        <v>358.6</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>343.96</v>
+      </c>
+      <c r="C520" t="n">
+        <v>348.29</v>
+      </c>
+      <c r="D520" t="n">
+        <v>358.94</v>
+      </c>
+      <c r="E520" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11324,7 +11366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B686"/>
+  <dimension ref="A1:B688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18187,6 +18229,26 @@
       </c>
       <c r="B686" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -18355,28 +18417,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1282939670141787</v>
+        <v>-0.1309637118293365</v>
       </c>
       <c r="J2" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K2" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06367880092838796</v>
+        <v>0.06645755791816921</v>
       </c>
       <c r="M2" t="n">
-        <v>2.742059607437085</v>
+        <v>2.743983901657399</v>
       </c>
       <c r="N2" t="n">
-        <v>11.83649032207724</v>
+        <v>11.83401445552314</v>
       </c>
       <c r="O2" t="n">
-        <v>3.44042007930387</v>
+        <v>3.440060240100911</v>
       </c>
       <c r="P2" t="n">
-        <v>350.4659525482263</v>
+        <v>350.497480915325</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18433,28 +18495,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1188702491798933</v>
+        <v>-0.1201949030363525</v>
       </c>
       <c r="J3" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K3" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07367701254891978</v>
+        <v>0.07567539204811946</v>
       </c>
       <c r="M3" t="n">
-        <v>2.369818857957365</v>
+        <v>2.36660297212082</v>
       </c>
       <c r="N3" t="n">
-        <v>8.688749558962389</v>
+        <v>8.667271363731089</v>
       </c>
       <c r="O3" t="n">
-        <v>2.947668495432007</v>
+        <v>2.944022989674349</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5239863500757</v>
+        <v>352.5396278912174</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18511,28 +18573,28 @@
         <v>0.0883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04933470752242481</v>
+        <v>0.04795390047925699</v>
       </c>
       <c r="J4" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K4" t="n">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01089503225904076</v>
+        <v>0.01037212878953453</v>
       </c>
       <c r="M4" t="n">
-        <v>2.626317037410475</v>
+        <v>2.622547408914383</v>
       </c>
       <c r="N4" t="n">
-        <v>10.82289606742831</v>
+        <v>10.79270117692525</v>
       </c>
       <c r="O4" t="n">
-        <v>3.289817026436016</v>
+        <v>3.285224676780151</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1805227621866</v>
+        <v>359.196824258001</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18570,7 +18632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E518"/>
+  <dimension ref="A1:E520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32555,6 +32617,60 @@
         </is>
       </c>
     </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-45.36910054774017,170.8645836830293</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-45.36970896957755,170.86463853899963</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-45.37024623855137,170.86510757278842</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-45.36910059922734,170.8645909591442</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-45.36970701456718,170.86465399414638</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-45.37024515520148,170.8651116319982</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
